--- a/template/quotation_template.xlsx
+++ b/template/quotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\04_Python×GPT\Projects\training\05_invoice_generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809A931D-447C-46E7-8B4C-03F179B38BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE12A4B-5214-4E17-A9EA-740738DD6812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27630" yWindow="1170" windowWidth="12735" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quotation" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>以下の通り、お見積り申し上げます。</t>
   </si>
@@ -40,20 +40,10 @@
     <t>合計金額（税込）</t>
   </si>
   <si>
-    <t>自社名</t>
-  </si>
-  <si>
     <t>東京都〇〇区〇〇1-2-3</t>
   </si>
   <si>
     <t>御見積書</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>振込期限</t>
-    <rPh sb="0" eb="2">
-      <t>フリコミ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -72,17 +62,52 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>担当　佐藤</t>
+    <t>TEL 12-3456-7890</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>小計</t>
     <rPh sb="0" eb="2">
-      <t>タントウ</t>
+      <t>ショウケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>消費税</t>
+    <rPh sb="0" eb="3">
+      <t>ショウヒゼイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>佐藤　国彦</t>
+    <rPh sb="0" eb="2">
+      <t>サトウ</t>
     </rPh>
     <rPh sb="3" eb="5">
-      <t>サトウ</t>
+      <t>クニヒコ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>TEL 12-3456-7890</t>
+    <t>E-Mail : m_sato@xxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有効期限</t>
+    <rPh sb="0" eb="2">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キゲン</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -162,7 +187,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -345,36 +370,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -383,11 +378,112 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -423,18 +519,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -746,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G35"/>
+  <dimension ref="A2:G43"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -759,46 +873,46 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="19"/>
-      <c r="C3" s="20"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
-      <c r="F5" s="17" t="s">
-        <v>6</v>
+      <c r="F5" s="15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
-      <c r="F6" s="17" t="s">
-        <v>7</v>
+      <c r="F6" s="15" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
-      <c r="F7" s="17" t="s">
-        <v>14</v>
+      <c r="F7" s="15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
-      <c r="F8" s="17" t="s">
-        <v>13</v>
+      <c r="F8" s="15" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
+      <c r="A9" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
@@ -808,34 +922,34 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="18"/>
+        <v>8</v>
+      </c>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="16"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="B15" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="B16" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="18"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B15" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B16" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="2:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="2:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B18" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>1</v>
@@ -962,11 +1076,52 @@
       <c r="E34" s="7"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="2:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E35" s="15" t="s">
+    <row r="35" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E35" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="18"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="E36" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="20"/>
+    </row>
+    <row r="37" spans="2:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="E37" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="16"/>
+      <c r="F37" s="22"/>
+    </row>
+    <row r="38" spans="2:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="25"/>
+      <c r="F40" s="26"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B41" s="25"/>
+      <c r="F41" s="26"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B42" s="25"/>
+      <c r="F42" s="26"/>
+    </row>
+    <row r="43" spans="2:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="27"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -977,7 +1132,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" display="tel:12-3456-7890" xr:uid="{1183B4A3-6261-435E-BE61-AA65E792ED56}"/>
+    <hyperlink ref="F7" r:id="rId1" display="tel:12-3456-7890" xr:uid="{7C9529F8-9E78-42DD-8A50-1C9A1051C222}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
